--- a/naver-place-crawler/results_health/세종_헬스장.xlsx
+++ b/naver-place-crawler/results_health/세종_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="Q2" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="R2" t="n">
-        <v>1373</v>
+        <v>1384</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>온어스피트니스 세종종촌점</t>
+          <t>온어스피트니스 헬스&amp;PT 세종종촌점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q3" t="n">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="R3" t="n">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>투모어휘트니스조치원9호점헬스PT</t>
+          <t>핫해짐 헬스&amp;PT 세종종촌점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2more_9@naver.com</t>
+          <t>fithaegym-sejong@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1449-4434</t>
+          <t>0507-1409-9930</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>세종 조치원읍 세종로 2282 5층 투모어 휘트니스</t>
+          <t>세종 도움3로 105-6 401,402호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/2more_fitness9/</t>
+          <t>https://www.instagram.com/lvj2_m/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5x3y2</t>
+          <t>https://talk.naver.com/ct/w5u1u8</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>411</v>
+        <v>228</v>
       </c>
       <c r="Q4" t="n">
-        <v>534</v>
+        <v>57</v>
       </c>
       <c r="R4" t="n">
-        <v>945</v>
+        <v>285</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1213463983</t>
+          <t>1881259445</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213463983</t>
+          <t>https://m.place.naver.com/place/1881259445</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>쏭프로GYM</t>
+          <t>골든타임핏 헬스 PT 조치원점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ssongprogym@naver.com</t>
+          <t>goldentime-fit_mc@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1382-8385</t>
+          <t>0507-1347-9684</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>세종 한누리대로 193 참미르빌딩 2층 202호</t>
+          <t>세종 조치원읍 세종로 2282 럭스스퀘어 6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssongprogym</t>
+          <t>https://www.instagram.com/gt_fit_jochiwon?igshid=YTQwZjQ0NmI0OA==</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w3dy11l</t>
+          <t>https://talk.naver.com/ct/w5t16y</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>273</v>
+        <v>1360</v>
       </c>
       <c r="Q5" t="n">
-        <v>404</v>
+        <v>203</v>
       </c>
       <c r="R5" t="n">
-        <v>677</v>
+        <v>1563</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1316527034</t>
+          <t>1058630917</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1316527034</t>
+          <t>https://m.place.naver.com/place/1058630917</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>핫해짐 헬스&amp;PT 세종종촌점</t>
+          <t>보람피트니스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fithaegym-sejong@naver.com</t>
+          <t>boram_fitness@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1409-9930</t>
+          <t>0507-1338-3134</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>세종 도움3로 105-6 401,402호</t>
+          <t>세종 호려울로 45 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lvj2_m/</t>
+          <t>https://blog.naver.com/boram_fitness</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5u1u8</t>
+          <t>https://talk.naver.com/ct/wi8qya7</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="Q6" t="n">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="R6" t="n">
-        <v>277</v>
+        <v>357</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1881259445</t>
+          <t>1766853986</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1881259445</t>
+          <t>https://m.place.naver.com/place/1766853986</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아이브 피트니스 헬스 &amp; PT</t>
+          <t>투모어휘트니스조치원9호점헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dlaeotn00@naver.com</t>
+          <t>2more_9@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1470-0860</t>
+          <t>0507-1449-4434</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>세종 시청대로 531 4층 전체</t>
+          <t>세종 조치원읍 세종로 2282 5층 투모어 휘트니스</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitness_iv</t>
+          <t>https://www.instagram.com/2more_fitness9/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wjsbr3a</t>
+          <t>https://talk.naver.com/ct/w5x3y2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>486</v>
+        <v>418</v>
       </c>
       <c r="Q7" t="n">
-        <v>123</v>
+        <v>542</v>
       </c>
       <c r="R7" t="n">
-        <v>609</v>
+        <v>960</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1878574714</t>
+          <t>1213463983</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1878574714</t>
+          <t>https://m.place.naver.com/place/1213463983</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>xowhd0918@naver.com</t>
+          <t>wuridongnaefitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q10" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R10" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1430,105 +1430,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>짐프레스&amp;필라립 소담점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>red881031@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1383-1228</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>세종 소담로 87 베스트탑 5층</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/red881031</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w3rmrr0</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>515</v>
-      </c>
-      <c r="R11" t="n">
-        <v>580</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2011557771</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2011557771</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/세종_헬스장.xlsx
+++ b/naver-place-crawler/results_health/세종_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="Q2" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R2" t="n">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q3" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="R3" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q4" t="n">
         <v>57</v>
       </c>
       <c r="R4" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="Q5" t="n">
         <v>203</v>
       </c>
       <c r="R5" t="n">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>보람피트니스</t>
+          <t>베이글짐 헬스&amp;PT 도담점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>boram_fitness@naver.com</t>
+          <t>baglegym1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1338-3134</t>
+          <t>0507-1366-9205</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>세종 호려울로 45 4층</t>
+          <t>세종 한누리대로 589 제3층 제302호, 제303호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/boram_fitness</t>
+          <t>https://www.instagram.com/bagel__gym/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi8qya7</t>
+          <t>https://talk.naver.com/ct/w7z62rj</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="Q6" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="R6" t="n">
-        <v>357</v>
+        <v>439</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1766853986</t>
+          <t>2000734130</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1766853986</t>
+          <t>https://m.place.naver.com/place/2000734130</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q7" t="n">
         <v>542</v>
       </c>
       <c r="R7" t="n">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마음바른휘트니스</t>
+          <t>나인원핏 헬스&amp;PT 세종나성점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>maumbarnfit@naver.com</t>
+          <t>2riwabang@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1390-0466</t>
+          <t>0507-1352-8382</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>세종 보듬3로 160 아이콤타워 5F</t>
+          <t>세종 한누리대로 316 세종마루2 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maumbarnfit</t>
+          <t>https://blog.naver.com/2riwabang/224083548666</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sy7b</t>
+          <t>https://talk.naver.com/ct/w4cwph</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>157</v>
+        <v>706</v>
       </c>
       <c r="Q8" t="n">
-        <v>477</v>
+        <v>882</v>
       </c>
       <c r="R8" t="n">
-        <v>634</v>
+        <v>1588</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1767406668</t>
+          <t>1575294603</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767406668</t>
+          <t>https://m.place.naver.com/place/1575294603</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1250,55 +1250,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스파렉스짐</t>
+          <t>마음바른휘트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unjungjoo@naver.com</t>
+          <t>maumbarnfit@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1341-7363</t>
+          <t>0507-1390-0466</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>세종 도움1로 106 메가시티 7층 스파렉스</t>
+          <t>세종 보듬3로 160 아이콤타워 5F</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://m.blog.naver.com/unjungjoo</t>
+          <t>https://www.instagram.com/maumbarnfit</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sy7b</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="Q9" t="n">
-        <v>192</v>
+        <v>477</v>
       </c>
       <c r="R9" t="n">
-        <v>260</v>
+        <v>634</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1114493197</t>
+          <t>1767406668</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1114493197</t>
+          <t>https://m.place.naver.com/place/1767406668</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1344,93 +1348,285 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>우리동네휘트니스</t>
+          <t>스파렉스짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wuridongnaefitness@naver.com</t>
+          <t>unjungjoo@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1341-7989</t>
+          <t>0507-1341-7363</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>세종 도움1로 106 메가시티 7층 스파렉스</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://m.blog.naver.com/unjungjoo</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>193</v>
+      </c>
+      <c r="R10" t="n">
+        <v>261</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1114493197</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1114493197</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>우리동네휘트니스</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>wuridongnaefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1341-7989</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>세종 호려울로 45 금남프라자 8층</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://litt.ly/woorifit_official</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w5y2mm</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>180</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q11" t="n">
         <v>98</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>278</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>1792064285</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1792064285</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>짐프레스&amp;필라립 소담점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>red881031@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1383-1228</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>세종 소담로 87 베스트탑 5층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/red881031</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3rmrr0</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>523</v>
+      </c>
+      <c r="R12" t="n">
+        <v>619</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2011557771</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2011557771</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/세종_헬스장.xlsx
+++ b/naver-place-crawler/results_health/세종_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="Q8" t="n">
         <v>882</v>
       </c>
       <c r="R8" t="n">
-        <v>1588</v>
+        <v>1593</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1437,39 +1437,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>우리동네휘트니스</t>
+          <t>짐프레스&amp;필라립 소담점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wuridongnaefitness@naver.com</t>
+          <t>red881031@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1341-7989</t>
+          <t>0507-1383-1228</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>세종 호려울로 45 금남프라자 8층</t>
+          <t>세종 소담로 87 베스트탑 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://litt.ly/woorifit_official</t>
+          <t>https://blog.naver.com/red881031</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5y2mm</t>
+          <t>https://talk.naver.com/ct/w3rmrr0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,17 +1499,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="Q11" t="n">
-        <v>98</v>
+        <v>523</v>
       </c>
       <c r="R11" t="n">
-        <v>278</v>
+        <v>619</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,113 +1518,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1792064285</t>
+          <t>2011557771</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1792064285</t>
+          <t>https://m.place.naver.com/place/2011557771</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>짐프레스&amp;필라립 소담점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>red881031@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1383-1228</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>세종 소담로 87 베스트탑 5층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/red881031</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w3rmrr0</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>96</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>523</v>
-      </c>
-      <c r="R12" t="n">
-        <v>619</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2011557771</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2011557771</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/세종_헬스장.xlsx
+++ b/naver-place-crawler/results_health/세종_헬스장.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -628,10 +628,10 @@
         <v>1059</v>
       </c>
       <c r="Q2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="R2" t="n">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>골든타임핏 헬스 PT 조치원점</t>
+          <t>베이글짐 헬스&amp;PT 도담점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>goldentime-fit_mc@naver.com</t>
+          <t>baglegym1@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1347-9684</t>
+          <t>0507-1366-9205</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>세종 조치원읍 세종로 2282 럭스스퀘어 6층</t>
+          <t>세종 한누리대로 589 제3층 제302호, 제303호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gt_fit_jochiwon?igshid=YTQwZjQ0NmI0OA==</t>
+          <t>https://www.instagram.com/bagel__gym/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5t16y</t>
+          <t>https://talk.naver.com/ct/w7z62rj</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1362</v>
+        <v>268</v>
       </c>
       <c r="Q5" t="n">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="R5" t="n">
-        <v>1565</v>
+        <v>440</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1058630917</t>
+          <t>2000734130</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058630917</t>
+          <t>https://m.place.naver.com/place/2000734130</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>베이글짐 헬스&amp;PT 도담점</t>
+          <t>골든타임핏 헬스 PT 조치원점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>baglegym1@naver.com</t>
+          <t>goldentime-fit_mc@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1366-9205</t>
+          <t>0507-1347-9684</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>세종 한누리대로 589 제3층 제302호, 제303호</t>
+          <t>세종 조치원읍 세종로 2282 럭스스퀘어 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bagel__gym/</t>
+          <t>https://www.instagram.com/gt_fit_jochiwon?igshid=YTQwZjQ0NmI0OA==</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7z62rj</t>
+          <t>https://talk.naver.com/ct/w5t16y</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>268</v>
+        <v>1362</v>
       </c>
       <c r="Q6" t="n">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="R6" t="n">
-        <v>439</v>
+        <v>1565</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2000734130</t>
+          <t>1058630917</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000734130</t>
+          <t>https://m.place.naver.com/place/1058630917</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>나인원핏 헬스&amp;PT 세종나성점</t>
+          <t>마음바른휘트니스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2riwabang@naver.com</t>
+          <t>maumbarnfit@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1352-8382</t>
+          <t>0507-1390-0466</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>세종 한누리대로 316 세종마루2 2층</t>
+          <t>세종 보듬3로 160 아이콤타워 5F</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/2riwabang/224083548666</t>
+          <t>https://www.instagram.com/maumbarnfit</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4cwph</t>
+          <t>https://talk.naver.com/ct/w4sy7b</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>711</v>
+        <v>157</v>
       </c>
       <c r="Q8" t="n">
-        <v>882</v>
+        <v>477</v>
       </c>
       <c r="R8" t="n">
-        <v>1593</v>
+        <v>634</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1575294603</t>
+          <t>1767406668</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1575294603</t>
+          <t>https://m.place.naver.com/place/1767406668</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,59 +1250,55 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마음바른휘트니스</t>
+          <t>스파렉스짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>maumbarnfit@naver.com</t>
+          <t>unjungjoo@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1390-0466</t>
+          <t>0507-1341-7363</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>세종 보듬3로 160 아이콤타워 5F</t>
+          <t>세종 도움1로 106 메가시티 7층 스파렉스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maumbarnfit</t>
+          <t>https://m.blog.naver.com/unjungjoo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4sy7b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="Q9" t="n">
-        <v>477</v>
+        <v>193</v>
       </c>
       <c r="R9" t="n">
-        <v>634</v>
+        <v>261</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1767406668</t>
+          <t>1114493197</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767406668</t>
+          <t>https://m.place.naver.com/place/1114493197</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1348,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스파렉스짐</t>
+          <t>우리동네휘트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unjungjoo@naver.com</t>
+          <t>wuridongnaefitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1341-7363</t>
+          <t>0507-1341-7989</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>세종 도움1로 106 메가시티 7층 스파렉스</t>
+          <t>세종 호려울로 45 금남프라자 8층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://m.blog.naver.com/unjungjoo</t>
+          <t>https://litt.ly/woorifit_official</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,20 +1376,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5y2mm</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="Q10" t="n">
-        <v>193</v>
+        <v>98</v>
       </c>
       <c r="R10" t="n">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1114493197</t>
+          <t>1792064285</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1114493197</t>
+          <t>https://m.place.naver.com/place/1792064285</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q11" t="n">
         <v>523</v>
       </c>
       <c r="R11" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/세종_헬스장.xlsx
+++ b/naver-place-crawler/results_health/세종_헬스장.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="Q2" t="n">
         <v>332</v>
       </c>
       <c r="R2" t="n">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q5" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R5" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q11" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="R11" t="n">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/세종_헬스장.xlsx
+++ b/naver-place-crawler/results_health/세종_헬스장.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마음바른휘트니스</t>
+          <t>나인원핏 헬스&amp;PT 세종나성점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>maumbarnfit@naver.com</t>
+          <t>2riwabang@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1390-0466</t>
+          <t>0507-1352-8382</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>세종 보듬3로 160 아이콤타워 5F</t>
+          <t>세종 한누리대로 316 세종마루2 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maumbarnfit</t>
+          <t>https://blog.naver.com/2riwabang/224083548666</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sy7b</t>
+          <t>https://talk.naver.com/ct/w4cwph</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>157</v>
+        <v>719</v>
       </c>
       <c r="Q8" t="n">
-        <v>477</v>
+        <v>882</v>
       </c>
       <c r="R8" t="n">
-        <v>634</v>
+        <v>1601</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1767406668</t>
+          <t>1575294603</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767406668</t>
+          <t>https://m.place.naver.com/place/1575294603</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1250,55 +1250,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스파렉스짐</t>
+          <t>마음바른휘트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unjungjoo@naver.com</t>
+          <t>maumbarnfit@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1341-7363</t>
+          <t>0507-1390-0466</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>세종 도움1로 106 메가시티 7층 스파렉스</t>
+          <t>세종 보듬3로 160 아이콤타워 5F</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://m.blog.naver.com/unjungjoo</t>
+          <t>https://www.instagram.com/maumbarnfit</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sy7b</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="Q9" t="n">
-        <v>193</v>
+        <v>477</v>
       </c>
       <c r="R9" t="n">
-        <v>261</v>
+        <v>634</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1114493197</t>
+          <t>1767406668</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1114493197</t>
+          <t>https://m.place.naver.com/place/1767406668</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1344,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>우리동네휘트니스</t>
+          <t>스파렉스짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wuridongnaefitness@naver.com</t>
+          <t>unjungjoo@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1341-7989</t>
+          <t>0507-1341-7363</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>세종 호려울로 45 금남프라자 8층</t>
+          <t>세종 도움1로 106 메가시티 7층 스파렉스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://litt.ly/woorifit_official</t>
+          <t>https://m.blog.naver.com/unjungjoo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,24 +1380,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5y2mm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="Q10" t="n">
-        <v>98</v>
+        <v>193</v>
       </c>
       <c r="R10" t="n">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1792064285</t>
+          <t>1114493197</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1792064285</t>
+          <t>https://m.place.naver.com/place/1114493197</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/세종_헬스장.xlsx
+++ b/naver-place-crawler/results_health/세종_헬스장.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -922,10 +922,10 @@
         <v>269</v>
       </c>
       <c r="Q5" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="R5" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>나인원핏 헬스&amp;PT 세종나성점</t>
+          <t>마음바른휘트니스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2riwabang@naver.com</t>
+          <t>maumbarnfit@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1352-8382</t>
+          <t>0507-1390-0466</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>세종 한누리대로 316 세종마루2 2층</t>
+          <t>세종 보듬3로 160 아이콤타워 5F</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/2riwabang/224083548666</t>
+          <t>https://www.instagram.com/maumbarnfit</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4cwph</t>
+          <t>https://talk.naver.com/ct/w4sy7b</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>719</v>
+        <v>157</v>
       </c>
       <c r="Q8" t="n">
-        <v>882</v>
+        <v>477</v>
       </c>
       <c r="R8" t="n">
-        <v>1601</v>
+        <v>634</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1575294603</t>
+          <t>1767406668</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1575294603</t>
+          <t>https://m.place.naver.com/place/1767406668</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,59 +1250,55 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마음바른휘트니스</t>
+          <t>스파렉스짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>maumbarnfit@naver.com</t>
+          <t>unjungjoo@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1390-0466</t>
+          <t>0507-1341-7363</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>세종 보듬3로 160 아이콤타워 5F</t>
+          <t>세종 도움1로 106 메가시티 7층 스파렉스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maumbarnfit</t>
+          <t>https://m.blog.naver.com/unjungjoo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4sy7b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="Q9" t="n">
-        <v>477</v>
+        <v>193</v>
       </c>
       <c r="R9" t="n">
-        <v>634</v>
+        <v>261</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1767406668</t>
+          <t>1114493197</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767406668</t>
+          <t>https://m.place.naver.com/place/1114493197</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1348,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스파렉스짐</t>
+          <t>우리동네휘트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unjungjoo@naver.com</t>
+          <t>wuridongnaefitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1341-7363</t>
+          <t>0507-1341-7989</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>세종 도움1로 106 메가시티 7층 스파렉스</t>
+          <t>세종 호려울로 45 금남프라자 8층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://m.blog.naver.com/unjungjoo</t>
+          <t>https://litt.ly/woorifit_official</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,20 +1376,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5y2mm</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="Q10" t="n">
-        <v>193</v>
+        <v>98</v>
       </c>
       <c r="R10" t="n">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1114493197</t>
+          <t>1792064285</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1114493197</t>
+          <t>https://m.place.naver.com/place/1792064285</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/세종_헬스장.xlsx
+++ b/naver-place-crawler/results_health/세종_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="Q2" t="n">
         <v>332</v>
       </c>
       <c r="R2" t="n">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         <v>98</v>
       </c>
       <c r="Q3" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R3" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q5" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="R5" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>투모어휘트니스조치원9호점헬스PT</t>
+          <t>나인원핏 헬스&amp;PT 세종나성점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2more_9@naver.com</t>
+          <t>2riwabang@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1449-4434</t>
+          <t>0507-1352-8382</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>세종 조치원읍 세종로 2282 5층 투모어 휘트니스</t>
+          <t>세종 한누리대로 316 세종마루2 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/2more_fitness9/</t>
+          <t>https://blog.naver.com/2riwabang/224083548666</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5x3y2</t>
+          <t>https://talk.naver.com/ct/w4cwph</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>419</v>
+        <v>719</v>
       </c>
       <c r="Q7" t="n">
-        <v>542</v>
+        <v>882</v>
       </c>
       <c r="R7" t="n">
-        <v>961</v>
+        <v>1601</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1213463983</t>
+          <t>1575294603</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213463983</t>
+          <t>https://m.place.naver.com/place/1575294603</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마음바른휘트니스</t>
+          <t>아이브 피트니스 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>maumbarnfit@naver.com</t>
+          <t>dlaeotn00@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1390-0466</t>
+          <t>0507-1470-0860</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>세종 보듬3로 160 아이콤타워 5F</t>
+          <t>세종 시청대로 531 4층 전체</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maumbarnfit</t>
+          <t>https://www.instagram.com/fitness_iv</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sy7b</t>
+          <t>https://talk.naver.com/ct/wjsbr3a</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>157</v>
+        <v>495</v>
       </c>
       <c r="Q8" t="n">
-        <v>477</v>
+        <v>130</v>
       </c>
       <c r="R8" t="n">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1767406668</t>
+          <t>1878574714</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767406668</t>
+          <t>https://m.place.naver.com/place/1878574714</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,55 +1250,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스파렉스짐</t>
+          <t>마음바른휘트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unjungjoo@naver.com</t>
+          <t>maumbarnfit@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1341-7363</t>
+          <t>0507-1390-0466</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>세종 도움1로 106 메가시티 7층 스파렉스</t>
+          <t>세종 보듬3로 160 아이콤타워 5F</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://m.blog.naver.com/unjungjoo</t>
+          <t>https://www.instagram.com/maumbarnfit</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sy7b</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="Q9" t="n">
-        <v>193</v>
+        <v>477</v>
       </c>
       <c r="R9" t="n">
-        <v>261</v>
+        <v>634</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1114493197</t>
+          <t>1767406668</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1114493197</t>
+          <t>https://m.place.naver.com/place/1767406668</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1437,96 +1441,190 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐프레스&amp;필라립 소담점</t>
+          <t>크로스핏퍼스트</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>red881031@naver.com</t>
+          <t>luhmei0914@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1383-1228</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>세종 나성로 125-10 902호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/crossfit1st</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w6bt9k1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>123</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>23</v>
+      </c>
+      <c r="R11" t="n">
+        <v>146</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1990522953</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1990522953</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>짐프레스&amp;필라립 소담점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>red881031@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1383-1228</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>세종 소담로 87 베스트탑 5층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://blog.naver.com/red881031</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w3rmrr0</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q12" t="n">
         <v>524</v>
       </c>
-      <c r="R11" t="n">
-        <v>622</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="R12" t="n">
+        <v>623</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>2011557771</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2011557771</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/세종_헬스장.xlsx
+++ b/naver-place-crawler/results_health/세종_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q3" t="n">
         <v>329</v>
       </c>
       <c r="R3" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q5" t="n">
         <v>177</v>
       </c>
       <c r="R5" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="Q6" t="n">
         <v>203</v>
       </c>
       <c r="R6" t="n">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="Q7" t="n">
         <v>882</v>
       </c>
       <c r="R7" t="n">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1528,105 +1528,203 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>짐프레스&amp;필라립 소담점</t>
+          <t>보람피트니스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>red881031@naver.com</t>
+          <t>boram_fitness@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1383-1228</t>
+          <t>0507-1338-3134</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>세종 호려울로 45 4층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/boram_fitness</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi8qya7</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>117</v>
+      </c>
+      <c r="R12" t="n">
+        <v>357</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1766853986</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1766853986</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>짐프레스&amp;필라립 소담점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>red881031@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1383-1228</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>세종 소담로 87 베스트탑 5층</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://blog.naver.com/red881031</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w3rmrr0</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>99</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q13" t="n">
         <v>524</v>
       </c>
-      <c r="R12" t="n">
-        <v>623</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="R13" t="n">
+        <v>625</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>2011557771</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2011557771</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/세종_헬스장.xlsx
+++ b/naver-place-crawler/results_health/세종_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -726,10 +726,10 @@
         <v>99</v>
       </c>
       <c r="Q3" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="R3" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q4" t="n">
         <v>57</v>
       </c>
       <c r="R4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q5" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R5" t="n">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>골든타임핏 헬스 PT 조치원점</t>
+          <t>F45 도담</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>goldentime-fit_mc@naver.com</t>
+          <t>dream5999@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1347-9684</t>
+          <t>070-4012-4562</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>세종 조치원읍 세종로 2282 럭스스퀘어 6층</t>
+          <t>세종 보듬3로 8-20 지하1층 102호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gt_fit_jochiwon?igshid=YTQwZjQ0NmI0OA==</t>
+          <t>https://www.instagram.com/f45_dodam/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5t16y</t>
+          <t>https://talk.naver.com/ct/w44f5y</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1366</v>
+        <v>1259</v>
       </c>
       <c r="Q6" t="n">
-        <v>203</v>
+        <v>120</v>
       </c>
       <c r="R6" t="n">
-        <v>1569</v>
+        <v>1379</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1058630917</t>
+          <t>1331400496</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058630917</t>
+          <t>https://m.place.naver.com/place/1331400496</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="Q7" t="n">
         <v>882</v>
       </c>
       <c r="R7" t="n">
-        <v>1602</v>
+        <v>1613</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q8" t="n">
         <v>130</v>
       </c>
       <c r="R8" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1343,39 +1343,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>우리동네휘트니스</t>
+          <t>짐프레스&amp;필라립 소담점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wuridongnaefitness@naver.com</t>
+          <t>red881031@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1341-7989</t>
+          <t>0507-1383-1228</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>세종 호려울로 45 금남프라자 8층</t>
+          <t>세종 소담로 87 베스트탑 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://litt.ly/woorifit_official</t>
+          <t>https://blog.naver.com/red881031</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5y2mm</t>
+          <t>https://talk.naver.com/ct/w3rmrr0</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,17 +1405,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>180</v>
+        <v>101</v>
       </c>
       <c r="Q10" t="n">
-        <v>98</v>
+        <v>525</v>
       </c>
       <c r="R10" t="n">
-        <v>278</v>
+        <v>626</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,305 +1424,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1792064285</t>
+          <t>2011557771</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1792064285</t>
+          <t>https://m.place.naver.com/place/2011557771</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>크로스핏퍼스트</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>luhmei0914@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>세종 나성로 125-10 902호</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://cafe.naver.com/crossfit1st</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w6bt9k1</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>123</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>23</v>
-      </c>
-      <c r="R11" t="n">
-        <v>146</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1990522953</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1990522953</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>보람피트니스</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>boram_fitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1338-3134</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>세종 호려울로 45 4층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/boram_fitness</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wi8qya7</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>240</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>117</v>
-      </c>
-      <c r="R12" t="n">
-        <v>357</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1766853986</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1766853986</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>짐프레스&amp;필라립 소담점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>red881031@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1383-1228</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>세종 소담로 87 베스트탑 5층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/red881031</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w3rmrr0</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>101</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>524</v>
-      </c>
-      <c r="R13" t="n">
-        <v>625</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2011557771</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2011557771</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/세종_헬스장.xlsx
+++ b/naver-place-crawler/results_health/세종_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="Q2" t="n">
         <v>332</v>
       </c>
       <c r="R2" t="n">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q5" t="n">
         <v>179</v>
       </c>
       <c r="R5" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="Q6" t="n">
         <v>120</v>
       </c>
       <c r="R6" t="n">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q8" t="n">
         <v>130</v>
       </c>
       <c r="R8" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1336,105 +1336,203 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐프레스&amp;필라립 소담점</t>
+          <t>우리동네휘트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>red881031@naver.com</t>
+          <t>wuridongnaefitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1383-1228</t>
+          <t>0507-1341-7989</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>세종 호려울로 45 금남프라자 8층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://litt.ly/woorifit_official</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5y2mm</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>98</v>
+      </c>
+      <c r="R10" t="n">
+        <v>279</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1792064285</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1792064285</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>짐프레스&amp;필라립 소담점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>red881031@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1383-1228</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>세종 소담로 87 베스트탑 5층</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://blog.naver.com/red881031</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w3rmrr0</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>101</v>
       </c>
-      <c r="Q10" t="n">
-        <v>525</v>
-      </c>
-      <c r="R10" t="n">
-        <v>626</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="Q11" t="n">
+        <v>526</v>
+      </c>
+      <c r="R11" t="n">
+        <v>627</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>2011557771</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2011557771</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/세종_헬스장.xlsx
+++ b/naver-place-crawler/results_health/세종_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q4" t="n">
         <v>57</v>
       </c>
       <c r="R4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="Q7" t="n">
         <v>882</v>
       </c>
       <c r="R7" t="n">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Q8" t="n">
         <v>130</v>
       </c>
       <c r="R8" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1343,39 +1343,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>우리동네휘트니스</t>
+          <t>짐프레스&amp;필라립 소담점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wuridongnaefitness@naver.com</t>
+          <t>red881031@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1341-7989</t>
+          <t>0507-1383-1228</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>세종 호려울로 45 금남프라자 8층</t>
+          <t>세종 소담로 87 베스트탑 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://litt.ly/woorifit_official</t>
+          <t>https://blog.naver.com/red881031</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5y2mm</t>
+          <t>https://talk.naver.com/ct/w3rmrr0</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,17 +1405,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>181</v>
+        <v>101</v>
       </c>
       <c r="Q10" t="n">
-        <v>98</v>
+        <v>526</v>
       </c>
       <c r="R10" t="n">
-        <v>279</v>
+        <v>627</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,113 +1424,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1792064285</t>
+          <t>2011557771</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1792064285</t>
+          <t>https://m.place.naver.com/place/2011557771</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>짐프레스&amp;필라립 소담점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>red881031@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1383-1228</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>세종 소담로 87 베스트탑 5층</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/red881031</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w3rmrr0</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>101</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>526</v>
-      </c>
-      <c r="R11" t="n">
-        <v>627</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2011557771</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2011557771</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
